--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>53739398</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
+        <v>83201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492093.7822272987</v>
+        <v>492094</v>
       </c>
       <c r="R2" t="n">
-        <v>6785440.563676572</v>
+        <v>6785441</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,19 +754,9 @@
           <t>2015-06-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84489811</v>
+        <v>58688618</v>
       </c>
       <c r="B3" t="n">
         <v>81972</v>
@@ -834,29 +824,24 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ångvasseln, Dlr</t>
+          <t>Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492074.3949425807</v>
+        <v>492093.7822272987</v>
       </c>
       <c r="R3" t="n">
-        <v>6785406.385121784</v>
+        <v>6785440.563676572</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +865,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-04-16</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -890,7 +875,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-04-16</t>
+          <t>2016-04-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -900,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växte i fin mossmatta vid granar precis intill vattnet ungefär där pricken är. Västra sidan av ån kollades inte vid besöket.</t>
+          <t>1 ex väster om Ångvasseln och 2 ex på östra sidan vid stigen mot bron. Förra året fanns flera ex intill några granstubbar/avverkade sedan ett par år. Idag sågs inga svampar alls där. Har de försvunnit på grund av avverkningen?</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84956522</v>
+        <v>84489811</v>
       </c>
       <c r="B4" t="n">
         <v>81972</v>
@@ -963,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -975,17 +960,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ångvasslans västsida, Dlr</t>
+          <t>Ångvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492074.9298841857</v>
+        <v>492074.3949425807</v>
       </c>
       <c r="R4" t="n">
-        <v>6785429.520109413</v>
+        <v>6785406.385121784</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +994,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
+          <t>2020-04-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1019,7 +1004,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
+          <t>2020-04-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1029,7 +1014,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>stora exemplar</t>
+          <t>Växte i fin mossmatta vid granar precis intill vattnet ungefär där pricken är. Västra sidan av ån kollades inte vid besöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,17 +1035,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Barbro Hellström</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107034047</v>
+        <v>84956522</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
+        <v>81972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,44 +1054,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ångvasslan, Dlr</t>
+          <t>Ångvasslans västsida, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492004.24917672</v>
+        <v>492074.9298841857</v>
       </c>
       <c r="R5" t="n">
-        <v>6785554.516679595</v>
+        <v>6785429.520109413</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,7 +1123,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1140,12 +1133,17 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>stora exemplar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,22 +1159,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer, Barbro Hellström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107034168</v>
+        <v>107034047</v>
       </c>
       <c r="B6" t="n">
-        <v>8377</v>
+        <v>77506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,47 +1183,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491932.6060607578</v>
+        <v>492004.24917672</v>
       </c>
       <c r="R6" t="n">
-        <v>6785468.404002112</v>
+        <v>6785554.516679595</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1295,7 +1287,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107034010</v>
+        <v>107034168</v>
       </c>
       <c r="B7" t="n">
         <v>8377</v>
@@ -1334,20 +1326,20 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492062.0959001349</v>
+        <v>491932.6060607578</v>
       </c>
       <c r="R7" t="n">
-        <v>6785518.2364193</v>
+        <v>6785468.404002112</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1417,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107034197</v>
+        <v>107034010</v>
       </c>
       <c r="B8" t="n">
-        <v>90155</v>
+        <v>8377</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,41 +1421,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>717</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491924.8089728337</v>
+        <v>492062.0959001349</v>
       </c>
       <c r="R8" t="n">
-        <v>6785436.609951376</v>
+        <v>6785518.2364193</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1517,21 +1515,6 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1548,10 +1531,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107034045</v>
+        <v>107034197</v>
       </c>
       <c r="B9" t="n">
-        <v>8377</v>
+        <v>90155</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,47 +1543,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>717</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492004.24917672</v>
+        <v>491924.8089728337</v>
       </c>
       <c r="R9" t="n">
-        <v>6785554.516679595</v>
+        <v>6785436.609951376</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1654,6 +1631,21 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1670,10 +1662,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107034063</v>
+        <v>107034045</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
+        <v>8377</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,37 +1678,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491908.8892294352</v>
+        <v>492004.24917672</v>
       </c>
       <c r="R10" t="n">
-        <v>6785441.466588384</v>
+        <v>6785554.516679595</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1786,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107038513</v>
+        <v>107034063</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
+        <v>89356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1802,32 +1800,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1835,10 +1827,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492093.6542446639</v>
+        <v>491908.8892294352</v>
       </c>
       <c r="R11" t="n">
-        <v>6785383.687394587</v>
+        <v>6785441.466588384</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1908,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108741957</v>
+        <v>107038513</v>
       </c>
       <c r="B12" t="n">
-        <v>89412</v>
+        <v>5113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,51 +1912,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stampvasseln, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492030.3563129686</v>
+        <v>492093.6542446639</v>
       </c>
       <c r="R12" t="n">
-        <v>6785571.80879466</v>
+        <v>6785383.687394587</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1988,22 +1979,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2012,28 +2003,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108742808</v>
+        <v>108741957</v>
       </c>
       <c r="B13" t="n">
-        <v>83054</v>
+        <v>89412</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2042,30 +2034,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1445</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2074,17 +2066,16 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stampvasseln vid Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Stampvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492106</v>
+        <v>492030.3563129686</v>
       </c>
       <c r="R13" t="n">
-        <v>6785401</v>
+        <v>6785571.80879466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2116,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2126,12 +2117,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tjäle i marken på de flesta ställen längs bäcken men inte just där murklorna växer. De ser ut att vara i tillväxtfas.</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,7 +2126,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108741490</v>
+        <v>108742808</v>
       </c>
       <c r="B14" t="n">
-        <v>57435</v>
+        <v>83054</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,44 +2156,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100077</v>
+        <v>1445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stampvasseln, Dlr</t>
+          <t>Stampvasseln vid Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492082.4438198795</v>
+        <v>492106</v>
       </c>
       <c r="R14" t="n">
-        <v>6785550.483710941</v>
+        <v>6785401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2240,7 +2230,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2250,7 +2240,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tjäle i marken på de flesta ställen längs bäcken men inte just där murklorna växer. De ser ut att vara i tillväxtfas.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2259,6 +2254,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2277,10 +2273,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111356613</v>
+        <v>108741490</v>
       </c>
       <c r="B15" t="n">
-        <v>88819</v>
+        <v>57435</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2289,38 +2285,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5685</v>
+        <v>100077</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnen, Dlr</t>
+          <t>Stampvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491932.6359417734</v>
+        <v>492082.4438198795</v>
       </c>
       <c r="R15" t="n">
-        <v>6785481.417835217</v>
+        <v>6785550.483710941</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2347,22 +2349,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2377,22 +2379,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111356614</v>
+        <v>111356613</v>
       </c>
       <c r="B16" t="n">
-        <v>96348</v>
+        <v>88819</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2401,45 +2403,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491909.0202035823</v>
+        <v>491932.6359417734</v>
       </c>
       <c r="R16" t="n">
-        <v>6785498.341940038</v>
+        <v>6785481.417835217</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2505,10 +2503,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111356612</v>
+        <v>111356614</v>
       </c>
       <c r="B17" t="n">
-        <v>90666</v>
+        <v>96348</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2517,41 +2515,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491951.0498785287</v>
+        <v>491909.0202035823</v>
       </c>
       <c r="R17" t="n">
-        <v>6785511.741186595</v>
+        <v>6785498.341940038</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2602,7 +2601,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2621,10 +2619,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111359889</v>
+        <v>111356612</v>
       </c>
       <c r="B18" t="n">
-        <v>95538</v>
+        <v>90666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,27 +2635,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2665,10 +2662,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491909.0202035823</v>
+        <v>491951.0498785287</v>
       </c>
       <c r="R18" t="n">
-        <v>6785498.341940038</v>
+        <v>6785511.741186595</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2738,10 +2735,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111491662</v>
+        <v>111359889</v>
       </c>
       <c r="B19" t="n">
-        <v>77515</v>
+        <v>95538</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2750,44 +2747,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491969.9043757546</v>
+        <v>491909.0202035823</v>
       </c>
       <c r="R19" t="n">
-        <v>6785523.747805699</v>
+        <v>6785498.341940038</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2811,7 +2809,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2821,7 +2819,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2842,22 +2840,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111491680</v>
+        <v>111491662</v>
       </c>
       <c r="B20" t="n">
-        <v>56414</v>
+        <v>77515</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2870,31 +2868,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2902,10 +2895,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491929.8523854768</v>
+        <v>491969.9043757546</v>
       </c>
       <c r="R20" t="n">
-        <v>6785530.587422797</v>
+        <v>6785523.747805699</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2956,6 +2949,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2974,10 +2968,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111491681</v>
+        <v>111491680</v>
       </c>
       <c r="B21" t="n">
-        <v>90666</v>
+        <v>56414</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2986,30 +2980,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3065,18 +3064,12 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>äldre fruktkreopp</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3095,7 +3088,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111491641</v>
+        <v>111491681</v>
       </c>
       <c r="B22" t="n">
         <v>90666</v>
@@ -3128,11 +3121,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3142,13 +3131,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491993.9996831641</v>
+        <v>491929.8523854768</v>
       </c>
       <c r="R22" t="n">
-        <v>6785505.377163783</v>
+        <v>6785530.587422797</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3192,7 +3181,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 4 platser i området</t>
+          <t>äldre fruktkreopp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3220,10 +3209,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111491657</v>
+        <v>111491641</v>
       </c>
       <c r="B23" t="n">
-        <v>89425</v>
+        <v>90666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3232,28 +3221,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3263,13 +3256,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491946.35724353</v>
+        <v>491993.9996831641</v>
       </c>
       <c r="R23" t="n">
-        <v>6785570.554389503</v>
+        <v>6785505.377163783</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3313,7 +3306,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>vid bohål</t>
+          <t>Minst 4 platser i området</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3341,10 +3334,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111491639</v>
+        <v>111491657</v>
       </c>
       <c r="B24" t="n">
-        <v>8377</v>
+        <v>89425</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3353,36 +3346,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3390,13 +3377,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491993.9996831641</v>
+        <v>491946.35724353</v>
       </c>
       <c r="R24" t="n">
-        <v>6785505.377163783</v>
+        <v>6785570.554389503</v>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3440,7 +3427,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Spridd och riklig i området</t>
+          <t>vid bohål</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3468,10 +3455,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111491685</v>
+        <v>111491639</v>
       </c>
       <c r="B25" t="n">
-        <v>88819</v>
+        <v>8377</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3484,26 +3471,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3511,13 +3504,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491909.4940688942</v>
+        <v>491993.9996831641</v>
       </c>
       <c r="R25" t="n">
-        <v>6785494.484901348</v>
+        <v>6785505.377163783</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3557,6 +3550,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spridd och riklig i området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3584,10 +3582,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111491649</v>
+        <v>111491685</v>
       </c>
       <c r="B26" t="n">
-        <v>90666</v>
+        <v>88819</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3600,21 +3598,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5685</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3627,10 +3625,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491979.6153062462</v>
+        <v>491909.4940688942</v>
       </c>
       <c r="R26" t="n">
-        <v>6785548.307010972</v>
+        <v>6785494.484901348</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3673,11 +3671,6 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>mycel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3705,10 +3698,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111612720</v>
+        <v>111491649</v>
       </c>
       <c r="B27" t="n">
-        <v>88924</v>
+        <v>90666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3721,28 +3714,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3752,13 +3741,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491993.9996831641</v>
+        <v>491979.6153062462</v>
       </c>
       <c r="R27" t="n">
-        <v>6785505.377163783</v>
+        <v>6785548.307010972</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3782,7 +3771,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3792,12 +3781,17 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3825,10 +3819,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111612738</v>
+        <v>111612720</v>
       </c>
       <c r="B28" t="n">
-        <v>56414</v>
+        <v>88924</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3837,35 +3831,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>256703</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3873,13 +3866,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491952.3910193561</v>
+        <v>491993.9996831641</v>
       </c>
       <c r="R28" t="n">
-        <v>6785464.984647369</v>
+        <v>6785505.377163783</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3927,6 +3920,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3945,10 +3939,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111612726</v>
+        <v>111612738</v>
       </c>
       <c r="B29" t="n">
-        <v>90168</v>
+        <v>56414</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3957,30 +3951,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>717</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4042,7 +4041,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4061,10 +4059,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111612736</v>
+        <v>111612726</v>
       </c>
       <c r="B30" t="n">
-        <v>56398</v>
+        <v>90168</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4073,35 +4071,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>717</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4163,6 +4156,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4181,10 +4175,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111682769</v>
+        <v>111612736</v>
       </c>
       <c r="B31" t="n">
-        <v>89980</v>
+        <v>56398</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4193,30 +4187,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1179</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4224,10 +4223,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491952</v>
+        <v>491952.3910193561</v>
       </c>
       <c r="R31" t="n">
-        <v>6785465</v>
+        <v>6785464.984647369</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4254,12 +4253,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4268,24 +4277,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4302,37 +4295,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111682658</v>
+        <v>111682769</v>
       </c>
       <c r="B32" t="n">
-        <v>91628</v>
+        <v>89980</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>1179</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4345,10 +4338,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492025</v>
+        <v>491952</v>
       </c>
       <c r="R32" t="n">
-        <v>6785567</v>
+        <v>6785465</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4383,11 +4376,6 @@
           <t>2023-08-25</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4397,6 +4385,21 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4413,14 +4416,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111682652</v>
+        <v>111682658</v>
       </c>
       <c r="B33" t="n">
-        <v>90709</v>
+        <v>91628</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4429,21 +4432,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4456,7 +4459,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492024</v>
+        <v>492025</v>
       </c>
       <c r="R33" t="n">
         <v>6785567</v>
@@ -4524,14 +4527,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111682655</v>
+        <v>111682652</v>
       </c>
       <c r="B34" t="n">
-        <v>91597</v>
+        <v>90709</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4540,28 +4543,24 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4571,7 +4570,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492025</v>
+        <v>492024</v>
       </c>
       <c r="R34" t="n">
         <v>6785567</v>
@@ -4639,14 +4638,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111682665</v>
+        <v>111682655</v>
       </c>
       <c r="B35" t="n">
-        <v>90682</v>
+        <v>91597</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4655,24 +4654,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4682,7 +4685,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492024</v>
+        <v>492025</v>
       </c>
       <c r="R35" t="n">
         <v>6785567</v>
@@ -4750,10 +4753,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112045406</v>
+        <v>111682665</v>
       </c>
       <c r="B36" t="n">
-        <v>90831</v>
+        <v>90682</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4784,20 +4787,22 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492044</v>
+        <v>492024</v>
       </c>
       <c r="R36" t="n">
-        <v>6785564</v>
+        <v>6785567</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4821,22 +4826,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4845,28 +4845,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112045302</v>
+        <v>112045406</v>
       </c>
       <c r="B37" t="n">
-        <v>90807</v>
+        <v>90831</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4879,21 +4880,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4910,7 +4911,7 @@
         <v>6785564</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4939,7 +4940,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4949,7 +4950,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4976,10 +4977,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112073422</v>
+        <v>112045302</v>
       </c>
       <c r="B38" t="n">
-        <v>89098</v>
+        <v>90807</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4988,44 +4989,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>233195</v>
+        <v>4361</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria neoformosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>sensu Schild</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N om Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491996</v>
+        <v>492044</v>
       </c>
       <c r="R38" t="n">
-        <v>6785531</v>
+        <v>6785564</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5055,60 +5051,49 @@
           <t>2023-09-12</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-09-12</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112073630</v>
+        <v>112073422</v>
       </c>
       <c r="B39" t="n">
-        <v>89073</v>
+        <v>89098</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5121,26 +5106,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>256703</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Tallfingersvamp</t>
-        </is>
+        <v>233195</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Ramaria neoformosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>sensu Schild</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5156,10 +5136,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491917</v>
+        <v>491996</v>
       </c>
       <c r="R39" t="n">
-        <v>6785497</v>
+        <v>6785531</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5239,10 +5219,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112045414</v>
+        <v>112073630</v>
       </c>
       <c r="B40" t="n">
-        <v>90838</v>
+        <v>89073</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5251,47 +5231,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
+          <t>N om Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492044</v>
+        <v>491917</v>
       </c>
       <c r="R40" t="n">
-        <v>6785564</v>
+        <v>6785497</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5318,42 +5303,171 @@
           <t>2023-09-12</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-09-12</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>112045414</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90838</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>492044</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6785564</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
+      <c r="AX41" t="inlineStr">
         <is>
           <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>53739398</v>
       </c>
       <c r="B2" t="n">
-        <v>83208</v>
+        <v>83222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -4178,7 +4178,7 @@
         <v>111612736</v>
       </c>
       <c r="B31" t="n">
-        <v>56398</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491952.3910193561</v>
+        <v>491952</v>
       </c>
       <c r="R31" t="n">
-        <v>6785464.984647369</v>
+        <v>6785465</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4256,19 +4256,9 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -4178,7 +4178,7 @@
         <v>111612736</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>58688618</v>
+        <v>84489811</v>
       </c>
       <c r="B3" t="n">
         <v>81972</v>
@@ -824,24 +824,29 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ångvasslan, Dlr</t>
+          <t>Ångvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492093.7822272987</v>
+        <v>492074.3949425807</v>
       </c>
       <c r="R3" t="n">
-        <v>6785440.563676572</v>
+        <v>6785406.385121784</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +870,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2020-04-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -875,7 +880,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-04-21</t>
+          <t>2020-04-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -885,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 ex väster om Ångvasseln och 2 ex på östra sidan vid stigen mot bron. Förra året fanns flera ex intill några granstubbar/avverkade sedan ett par år. Idag sågs inga svampar alls där. Har de försvunnit på grund av avverkningen?</t>
+          <t>Växte i fin mossmatta vid granar precis intill vattnet ungefär där pricken är. Västra sidan av ån kollades inte vid besöket.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84489811</v>
+        <v>84956522</v>
       </c>
       <c r="B4" t="n">
         <v>81972</v>
@@ -948,7 +953,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -960,17 +965,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ångvasseln, Dlr</t>
+          <t>Ångvasslans västsida, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492074.3949425807</v>
+        <v>492074.9298841857</v>
       </c>
       <c r="R4" t="n">
-        <v>6785406.385121784</v>
+        <v>6785429.520109413</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +999,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-04-16</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1004,7 +1009,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-04-16</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1014,7 +1019,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växte i fin mossmatta vid granar precis intill vattnet ungefär där pricken är. Västra sidan av ån kollades inte vid besöket.</t>
+          <t>stora exemplar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,17 +1040,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Barbro Hellström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>84956522</v>
+        <v>107034047</v>
       </c>
       <c r="B5" t="n">
-        <v>81972</v>
+        <v>77506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,52 +1059,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1445</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ångvasslans västsida, Dlr</t>
+          <t>Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492074.9298841857</v>
+        <v>492004.24917672</v>
       </c>
       <c r="R5" t="n">
-        <v>6785429.520109413</v>
+        <v>6785554.516679595</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,7 +1120,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1133,17 +1130,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>stora exemplar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,22 +1151,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Barbro Hellström</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107034047</v>
+        <v>107034168</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
+        <v>8377</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,41 +1175,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492004.24917672</v>
+        <v>491932.6060607578</v>
       </c>
       <c r="R6" t="n">
-        <v>6785554.516679595</v>
+        <v>6785468.404002112</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1287,7 +1285,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107034168</v>
+        <v>107034010</v>
       </c>
       <c r="B7" t="n">
         <v>8377</v>
@@ -1326,20 +1324,20 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491932.6060607578</v>
+        <v>492062.0959001349</v>
       </c>
       <c r="R7" t="n">
-        <v>6785468.404002112</v>
+        <v>6785518.2364193</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1409,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107034010</v>
+        <v>107034197</v>
       </c>
       <c r="B8" t="n">
-        <v>8377</v>
+        <v>90155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,47 +1419,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>717</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492062.0959001349</v>
+        <v>491924.8089728337</v>
       </c>
       <c r="R8" t="n">
-        <v>6785518.2364193</v>
+        <v>6785436.609951376</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1515,6 +1507,21 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1531,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107034197</v>
+        <v>107034045</v>
       </c>
       <c r="B9" t="n">
-        <v>90155</v>
+        <v>8377</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,41 +1550,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>717</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491924.8089728337</v>
+        <v>492004.24917672</v>
       </c>
       <c r="R9" t="n">
-        <v>6785436.609951376</v>
+        <v>6785554.516679595</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1631,21 +1644,6 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1662,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107034045</v>
+        <v>107034063</v>
       </c>
       <c r="B10" t="n">
-        <v>8377</v>
+        <v>89356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,43 +1676,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492004.24917672</v>
+        <v>491908.8892294352</v>
       </c>
       <c r="R10" t="n">
-        <v>6785554.516679595</v>
+        <v>6785441.466588384</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1784,10 +1776,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107034063</v>
+        <v>107038513</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
+        <v>5113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,26 +1792,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1827,10 +1825,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491908.8892294352</v>
+        <v>492093.6542446639</v>
       </c>
       <c r="R11" t="n">
-        <v>6785441.466588384</v>
+        <v>6785383.687394587</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1900,10 +1898,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107038513</v>
+        <v>108741957</v>
       </c>
       <c r="B12" t="n">
-        <v>5113</v>
+        <v>89412</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,50 +1910,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Stampvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492093.6542446639</v>
+        <v>492030.3563129686</v>
       </c>
       <c r="R12" t="n">
-        <v>6785383.687394587</v>
+        <v>6785571.80879466</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1979,22 +1978,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2003,29 +2002,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108741957</v>
+        <v>108742808</v>
       </c>
       <c r="B13" t="n">
-        <v>89412</v>
+        <v>83054</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2034,30 +2032,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>1445</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2066,16 +2064,17 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stampvasseln, Dlr</t>
+          <t>Stampvasseln vid Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492030.3563129686</v>
+        <v>492106</v>
       </c>
       <c r="R13" t="n">
-        <v>6785571.80879466</v>
+        <v>6785401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,7 +2106,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,7 +2116,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tjäle i marken på de flesta ställen längs bäcken men inte just där murklorna växer. De ser ut att vara i tillväxtfas.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2126,6 +2130,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2144,10 +2149,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108742808</v>
+        <v>108741490</v>
       </c>
       <c r="B14" t="n">
-        <v>83054</v>
+        <v>57435</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2156,49 +2161,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1445</v>
+        <v>100077</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stampvasseln vid Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Stampvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492106</v>
+        <v>492082.4438198795</v>
       </c>
       <c r="R14" t="n">
-        <v>6785401</v>
+        <v>6785550.483710941</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2240,12 +2240,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tjäle i marken på de flesta ställen längs bäcken men inte just där murklorna växer. De ser ut att vara i tillväxtfas.</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2254,7 +2249,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2273,10 +2267,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108741490</v>
+        <v>111356613</v>
       </c>
       <c r="B15" t="n">
-        <v>57435</v>
+        <v>88819</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2285,44 +2279,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100077</v>
+        <v>5685</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stampvasseln, Dlr</t>
+          <t>Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492082.4438198795</v>
+        <v>491932.6359417734</v>
       </c>
       <c r="R15" t="n">
-        <v>6785550.483710941</v>
+        <v>6785481.417835217</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2349,22 +2337,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2379,22 +2367,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111356613</v>
+        <v>111356614</v>
       </c>
       <c r="B16" t="n">
-        <v>88819</v>
+        <v>96348</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2403,41 +2391,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5685</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491932.6359417734</v>
+        <v>491909.0202035823</v>
       </c>
       <c r="R16" t="n">
-        <v>6785481.417835217</v>
+        <v>6785498.341940038</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2503,10 +2495,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111356614</v>
+        <v>111356612</v>
       </c>
       <c r="B17" t="n">
-        <v>96348</v>
+        <v>90666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,42 +2507,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491909.0202035823</v>
+        <v>491951.0498785287</v>
       </c>
       <c r="R17" t="n">
-        <v>6785498.341940038</v>
+        <v>6785511.741186595</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2601,6 +2592,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2619,10 +2611,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111356612</v>
+        <v>111359889</v>
       </c>
       <c r="B18" t="n">
-        <v>90666</v>
+        <v>95538</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2635,26 +2627,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2662,10 +2655,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491951.0498785287</v>
+        <v>491909.0202035823</v>
       </c>
       <c r="R18" t="n">
-        <v>6785511.741186595</v>
+        <v>6785498.341940038</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2735,10 +2728,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111359889</v>
+        <v>111491662</v>
       </c>
       <c r="B19" t="n">
-        <v>95538</v>
+        <v>77515</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2747,45 +2740,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långtjärnen, Dlr</t>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491909.0202035823</v>
+        <v>491969.9043757546</v>
       </c>
       <c r="R19" t="n">
-        <v>6785498.341940038</v>
+        <v>6785523.747805699</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2809,7 +2801,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2819,7 +2811,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2840,22 +2832,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111491662</v>
+        <v>111491680</v>
       </c>
       <c r="B20" t="n">
-        <v>77515</v>
+        <v>56414</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2868,26 +2860,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2895,10 +2892,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491969.9043757546</v>
+        <v>491929.8523854768</v>
       </c>
       <c r="R20" t="n">
-        <v>6785523.747805699</v>
+        <v>6785530.587422797</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2949,7 +2946,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2968,10 +2964,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111491680</v>
+        <v>111491681</v>
       </c>
       <c r="B21" t="n">
-        <v>56414</v>
+        <v>90666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2980,35 +2976,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3064,12 +3055,18 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre fruktkreopp</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3088,7 +3085,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111491681</v>
+        <v>111491641</v>
       </c>
       <c r="B22" t="n">
         <v>90666</v>
@@ -3121,7 +3118,11 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3131,13 +3132,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491929.8523854768</v>
+        <v>491993.9996831641</v>
       </c>
       <c r="R22" t="n">
-        <v>6785530.587422797</v>
+        <v>6785505.377163783</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3181,7 +3182,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>äldre fruktkreopp</t>
+          <t>Minst 4 platser i området</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3209,10 +3210,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111491641</v>
+        <v>111491657</v>
       </c>
       <c r="B23" t="n">
-        <v>90666</v>
+        <v>89425</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3221,32 +3222,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3256,13 +3253,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491993.9996831641</v>
+        <v>491946.35724353</v>
       </c>
       <c r="R23" t="n">
-        <v>6785505.377163783</v>
+        <v>6785570.554389503</v>
       </c>
       <c r="S23" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3306,7 +3303,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 4 platser i området</t>
+          <t>vid bohål</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3334,10 +3331,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111491657</v>
+        <v>111491639</v>
       </c>
       <c r="B24" t="n">
-        <v>89425</v>
+        <v>8377</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3346,30 +3343,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3377,13 +3380,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491946.35724353</v>
+        <v>491993.9996831641</v>
       </c>
       <c r="R24" t="n">
-        <v>6785570.554389503</v>
+        <v>6785505.377163783</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3427,7 +3430,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>vid bohål</t>
+          <t>Spridd och riklig i området</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3455,10 +3458,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111491639</v>
+        <v>111491685</v>
       </c>
       <c r="B25" t="n">
-        <v>8377</v>
+        <v>88819</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3471,32 +3474,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3504,13 +3501,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491993.9996831641</v>
+        <v>491909.4940688942</v>
       </c>
       <c r="R25" t="n">
-        <v>6785505.377163783</v>
+        <v>6785494.484901348</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3550,11 +3547,6 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spridd och riklig i området</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3582,10 +3574,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111491685</v>
+        <v>111491649</v>
       </c>
       <c r="B26" t="n">
-        <v>88819</v>
+        <v>90666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3598,21 +3590,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3625,10 +3617,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491909.4940688942</v>
+        <v>491979.6153062462</v>
       </c>
       <c r="R26" t="n">
-        <v>6785494.484901348</v>
+        <v>6785548.307010972</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3671,6 +3663,11 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3698,10 +3695,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111491649</v>
+        <v>111612720</v>
       </c>
       <c r="B27" t="n">
-        <v>90666</v>
+        <v>88924</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3714,24 +3711,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3741,13 +3742,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491979.6153062462</v>
+        <v>491993.9996831641</v>
       </c>
       <c r="R27" t="n">
-        <v>6785548.307010972</v>
+        <v>6785505.377163783</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3771,7 +3772,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3781,17 +3782,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>mycel</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3819,10 +3815,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111612720</v>
+        <v>111612738</v>
       </c>
       <c r="B28" t="n">
-        <v>88924</v>
+        <v>56414</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3831,34 +3827,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>256703</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3866,13 +3863,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491993.9996831641</v>
+        <v>491952.3910193561</v>
       </c>
       <c r="R28" t="n">
-        <v>6785505.377163783</v>
+        <v>6785464.984647369</v>
       </c>
       <c r="S28" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3920,7 +3917,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3939,10 +3935,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111612738</v>
+        <v>111612726</v>
       </c>
       <c r="B29" t="n">
-        <v>56414</v>
+        <v>90168</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3951,35 +3947,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>717</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4041,6 +4032,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4059,10 +4051,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111612726</v>
+        <v>111612736</v>
       </c>
       <c r="B30" t="n">
-        <v>90168</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4071,30 +4063,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>717</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4102,10 +4099,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491952.3910193561</v>
+        <v>491952</v>
       </c>
       <c r="R30" t="n">
-        <v>6785464.984647369</v>
+        <v>6785465</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4135,28 +4132,17 @@
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-08-21</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4175,10 +4161,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111612736</v>
+        <v>111682769</v>
       </c>
       <c r="B31" t="n">
-        <v>57481</v>
+        <v>89980</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4187,35 +4173,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1179</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4253,12 +4234,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4267,8 +4248,24 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4285,37 +4282,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111682769</v>
+        <v>111682658</v>
       </c>
       <c r="B32" t="n">
-        <v>89980</v>
+        <v>91628</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1179</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4328,10 +4325,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491952</v>
+        <v>492025</v>
       </c>
       <c r="R32" t="n">
-        <v>6785465</v>
+        <v>6785567</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4366,6 +4363,11 @@
           <t>2023-08-25</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4375,21 +4377,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4406,14 +4393,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111682658</v>
+        <v>111682652</v>
       </c>
       <c r="B33" t="n">
-        <v>91628</v>
+        <v>90709</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4422,21 +4409,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4449,7 +4436,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492025</v>
+        <v>492024</v>
       </c>
       <c r="R33" t="n">
         <v>6785567</v>
@@ -4517,14 +4504,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111682652</v>
+        <v>111682655</v>
       </c>
       <c r="B34" t="n">
-        <v>90709</v>
+        <v>91597</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4533,24 +4520,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4560,7 +4551,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492024</v>
+        <v>492025</v>
       </c>
       <c r="R34" t="n">
         <v>6785567</v>
@@ -4628,14 +4619,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111682655</v>
+        <v>111682665</v>
       </c>
       <c r="B35" t="n">
-        <v>91597</v>
+        <v>90682</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4644,28 +4635,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4675,7 +4662,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492025</v>
+        <v>492024</v>
       </c>
       <c r="R35" t="n">
         <v>6785567</v>
@@ -4743,10 +4730,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111682665</v>
+        <v>112045406</v>
       </c>
       <c r="B36" t="n">
-        <v>90682</v>
+        <v>90831</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4777,22 +4764,20 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492024</v>
+        <v>492044</v>
       </c>
       <c r="R36" t="n">
-        <v>6785567</v>
+        <v>6785564</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4816,17 +4801,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4835,29 +4825,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112045406</v>
+        <v>112045302</v>
       </c>
       <c r="B37" t="n">
-        <v>90831</v>
+        <v>90807</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4870,21 +4859,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4901,7 +4890,7 @@
         <v>6785564</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4930,7 +4919,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4940,7 +4929,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4967,10 +4956,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112045302</v>
+        <v>112073422</v>
       </c>
       <c r="B38" t="n">
-        <v>90807</v>
+        <v>89098</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4979,39 +4968,44 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
+        <v>233195</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria neoformosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>sensu Schild</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
+          <t>N om Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492044</v>
+        <v>491996</v>
       </c>
       <c r="R38" t="n">
-        <v>6785564</v>
+        <v>6785531</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5041,49 +5035,60 @@
           <t>2023-09-12</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-09-12</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
+          <t>Janolof Hermansson, Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112073422</v>
+        <v>112073630</v>
       </c>
       <c r="B39" t="n">
-        <v>89098</v>
+        <v>89073</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5096,21 +5101,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>233195</v>
+        <v>256703</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria neoformosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>sensu Schild</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5126,10 +5136,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491996</v>
+        <v>491917</v>
       </c>
       <c r="R39" t="n">
-        <v>6785531</v>
+        <v>6785497</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5209,10 +5219,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112073630</v>
+        <v>112045414</v>
       </c>
       <c r="B40" t="n">
-        <v>89073</v>
+        <v>90838</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5221,52 +5231,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N om Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491917</v>
+        <v>492044</v>
       </c>
       <c r="R40" t="n">
-        <v>6785497</v>
+        <v>6785564</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5293,171 +5298,42 @@
           <t>2023-09-12</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-09-12</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>112045414</v>
-      </c>
-      <c r="B41" t="n">
-        <v>90838</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>492044</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6785564</v>
-      </c>
-      <c r="S41" t="n">
-        <v>15</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5335,6 +5335,103 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128919219</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92786</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>491914</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6785535</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Björk, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5431,6 +5431,103 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129335247</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90571</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Övre Tetvasseltjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>491964</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6785555</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Agnes Rengren, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>129335247</v>
       </c>
       <c r="B42" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92813</v>
+        <v>92814</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92814</v>
+        <v>92817</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>129335247</v>
       </c>
       <c r="B42" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>129335247</v>
       </c>
       <c r="B42" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5340,7 +5340,7 @@
         <v>128919219</v>
       </c>
       <c r="B41" t="n">
-        <v>92819</v>
+        <v>92823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>129335247</v>
       </c>
       <c r="B42" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5437,7 +5437,7 @@
         <v>129335247</v>
       </c>
       <c r="B42" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5437,7 +5437,7 @@
         <v>129335247</v>
       </c>
       <c r="B42" t="n">
-        <v>90582</v>
+        <v>90585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5437,7 +5437,7 @@
         <v>129335247</v>
       </c>
       <c r="B42" t="n">
-        <v>90585</v>
+        <v>90613</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5437,7 +5437,7 @@
         <v>129335247</v>
       </c>
       <c r="B42" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5437,7 +5437,7 @@
         <v>129335247</v>
       </c>
       <c r="B42" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Agnes Rengren, Anton Björk</t>
+          <t>Anton Björk, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5437,7 +5437,7 @@
         <v>129335247</v>
       </c>
       <c r="B42" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Björk, Agnes Rengren</t>
+          <t>Agnes Rengren, Anton Björk</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -5534,7 +5534,7 @@
         <v>132837441</v>
       </c>
       <c r="B43" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53739398</v>
+        <v>107034197</v>
       </c>
       <c r="B2" t="n">
-        <v>83222</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1445</v>
+        <v>717</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Schwein. : Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492094</v>
+        <v>491925</v>
       </c>
       <c r="R2" t="n">
-        <v>6785441</v>
+        <v>6785437</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,17 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-02</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>De växte intill  tre grova granar intill Ångvasseln, eller snarare stubbar då träden var avverkade. Radien på växtplatsen några meter. Jag fick tipset av Sigurd Jönsson och han hade i sin tur fått det av en man och en pojke. Pojken hade lekt med pinnar. Senare läste de om fyndet vid Oreälven i Mora Tidning  i förra veckan  och förstod då att de sett bombmurkla.</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,30 +761,40 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84489811</v>
+        <v>111612726</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,48 +802,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1445</v>
+        <v>717</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein. : Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ångvasseln, Dlr</t>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492074.3949425807</v>
+        <v>491952</v>
       </c>
       <c r="R3" t="n">
-        <v>6785406.385121784</v>
+        <v>6785465</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,27 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-04-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-04-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växte i fin mossmatta vid granar precis intill vattnet ungefär där pricken är. Västra sidan av ån kollades inte vid besöket.</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,15 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84956522</v>
+        <v>112045817</v>
       </c>
       <c r="B4" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,48 +903,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1445</v>
+        <v>717</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein. : Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ångvasslans västsida, Dlr</t>
+          <t>Stampvasseln, Stampvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492074.9298841857</v>
+        <v>492008</v>
       </c>
       <c r="R4" t="n">
-        <v>6785429.520109413</v>
+        <v>6785598</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,27 +958,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>stora exemplar</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,56 +982,50 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Barbro Hellström</t>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107034047</v>
+        <v>111682769</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,17 +1034,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ångvasslan, Dlr</t>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492004.24917672</v>
+        <v>491952</v>
       </c>
       <c r="R5" t="n">
-        <v>6785554.516679595</v>
+        <v>6785465</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,22 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,77 +1086,84 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107034168</v>
+        <v>53739398</v>
       </c>
       <c r="B6" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>1445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491932.6060607578</v>
+        <v>492094</v>
       </c>
       <c r="R6" t="n">
-        <v>6785468.404002112</v>
+        <v>6785441</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,22 +1187,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>De växte intill  tre grova granar intill Ångvasseln, eller snarare stubbar då träden var avverkade. Radien på växtplatsen några meter. Jag fick tipset av Sigurd Jönsson och han hade i sin tur fått det av en man och en pojke. Pojken hade lekt med pinnar. Senare läste de om fyndet vid Oreälven i Mora Tidning  i förra veckan  och förstod då att de sett bombmurkla.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,71 +1213,68 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107034010</v>
+        <v>84489811</v>
       </c>
       <c r="B7" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>1445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ångvasslan, Dlr</t>
+          <t>Ångvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492062.0959001349</v>
+        <v>492074</v>
       </c>
       <c r="R7" t="n">
-        <v>6785518.2364193</v>
+        <v>6785406</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1364,22 +1301,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växte i fin mossmatta vid granar precis intill vattnet ungefär där pricken är. Västra sidan av ån kollades inte vid besöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,68 +1327,71 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107034197</v>
+        <v>84956522</v>
       </c>
       <c r="B8" t="n">
-        <v>90155</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>717</v>
+        <v>1445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Ångvasslans västsida, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491924.8089728337</v>
+        <v>492075</v>
       </c>
       <c r="R8" t="n">
-        <v>6785436.609951376</v>
+        <v>6785430</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,22 +1415,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>stora exemplar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,78 +1438,60 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer, Barbro Hellström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107034045</v>
+        <v>84956539</v>
       </c>
       <c r="B9" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>1445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1587,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492004.24917672</v>
+        <v>492048</v>
       </c>
       <c r="R9" t="n">
-        <v>6785554.516679595</v>
+        <v>6785388</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1617,22 +1529,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>små exemplar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,68 +1555,71 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer, Barbro Hellström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107034063</v>
+        <v>108742808</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Stampvasseln vid Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491908.8892294352</v>
+        <v>492106</v>
       </c>
       <c r="R10" t="n">
-        <v>6785441.466588384</v>
+        <v>6785401</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1733,22 +1643,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tjäle i marken på de flesta ställen längs bäcken men inte just där murklorna växer. De ser ut att vara i tillväxtfas.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,74 +1679,71 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107038513</v>
+        <v>132360245</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>1445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492093.6542446639</v>
+        <v>492050</v>
       </c>
       <c r="R11" t="n">
-        <v>6785383.687394587</v>
+        <v>6785392</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1855,22 +1767,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1886,72 +1798,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Hanna Mårshagen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Hanna Mårshagen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108741957</v>
+        <v>128918470</v>
       </c>
       <c r="B12" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>1958</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stampvasseln, Dlr</t>
+          <t>Nedre Tetvasseltjärn, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492030.3563129686</v>
+        <v>492010</v>
       </c>
       <c r="R12" t="n">
-        <v>6785571.80879466</v>
+        <v>6785588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,22 +1875,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:53</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:53</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2008,73 +1895,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Anton Björk, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108742808</v>
+        <v>129335247</v>
       </c>
       <c r="B13" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1445</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stampvasseln vid Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Övre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492106</v>
+        <v>491964</v>
       </c>
       <c r="R13" t="n">
-        <v>6785401</v>
+        <v>6785555</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2101,27 +1972,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>19:06</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tjäle i marken på de flesta ställen längs bäcken men inte just där murklorna växer. De ser ut att vara i tillväxtfas.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2130,75 +1986,66 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Agnes Rengren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Agnes Rengren, Anton Björk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108741490</v>
+        <v>111682665</v>
       </c>
       <c r="B14" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100077</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stampvasseln, Dlr</t>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492082.4438198795</v>
+        <v>492025</v>
       </c>
       <c r="R14" t="n">
-        <v>6785550.483710941</v>
+        <v>6785567</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2225,22 +2072,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:39</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:39</t>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,71 +2091,68 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111356613</v>
+        <v>112045406</v>
       </c>
       <c r="B15" t="n">
-        <v>88819</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5685</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnen, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491932.6359417734</v>
+        <v>492045</v>
       </c>
       <c r="R15" t="n">
-        <v>6785481.417835217</v>
+        <v>6785564</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2337,22 +2176,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2367,69 +2206,67 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111356614</v>
+        <v>111682655</v>
       </c>
       <c r="B16" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnen, Dlr</t>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491909.0202035823</v>
+        <v>492025</v>
       </c>
       <c r="R16" t="n">
-        <v>6785498.341940038</v>
+        <v>6785567</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2453,22 +2290,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2477,74 +2309,68 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111356612</v>
+        <v>112045302</v>
       </c>
       <c r="B17" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnen, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491951.0498785287</v>
+        <v>492045</v>
       </c>
       <c r="R17" t="n">
-        <v>6785511.741186595</v>
+        <v>6785564</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2568,22 +2394,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2592,76 +2418,76 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111359889</v>
+        <v>112045425</v>
       </c>
       <c r="B18" t="n">
-        <v>95538</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnen, Dlr</t>
+          <t>Stampvasseln, Stampvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491909.0202035823</v>
+        <v>492008</v>
       </c>
       <c r="R18" t="n">
-        <v>6785498.341940038</v>
+        <v>6785598</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2685,22 +2511,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2709,34 +2535,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111491662</v>
+        <v>128919219</v>
       </c>
       <c r="B19" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,40 +2564,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491969.9043757546</v>
+        <v>491914</v>
       </c>
       <c r="R19" t="n">
-        <v>6785523.747805699</v>
+        <v>6785535</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2801,22 +2618,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2825,34 +2632,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111491680</v>
+        <v>111356612</v>
       </c>
       <c r="B20" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,45 +2661,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491929.8523854768</v>
+        <v>491951</v>
       </c>
       <c r="R20" t="n">
-        <v>6785530.587422797</v>
+        <v>6785512</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2922,22 +2718,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2946,37 +2732,33 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111491681</v>
+        <v>111491649</v>
       </c>
       <c r="B21" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3007,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491929.8523854768</v>
+        <v>491979</v>
       </c>
       <c r="R21" t="n">
-        <v>6785530.587422797</v>
+        <v>6785548</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3040,24 +2822,14 @@
           <t>2023-08-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-08-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>äldre fruktkreopp</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,19 +2857,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111491641</v>
+        <v>111491681</v>
       </c>
       <c r="B22" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3118,11 +2885,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3132,13 +2895,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491993.9996831641</v>
+        <v>491930</v>
       </c>
       <c r="R22" t="n">
-        <v>6785505.377163783</v>
+        <v>6785530</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3165,24 +2928,14 @@
           <t>2023-08-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-08-15</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 4 platser i området</t>
+          <t>äldre fruktkreopp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3210,56 +2963,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111491657</v>
+        <v>128918765</v>
       </c>
       <c r="B23" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>4365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärn, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491946.35724353</v>
+        <v>491967</v>
       </c>
       <c r="R23" t="n">
-        <v>6785570.554389503</v>
+        <v>6785592</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3283,27 +3028,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>vid bohål</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3312,81 +3042,76 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111491639</v>
+        <v>112045503</v>
       </c>
       <c r="B24" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>4745</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Stampvasseln, Stampvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491993.9996831641</v>
+        <v>492008</v>
       </c>
       <c r="R24" t="n">
-        <v>6785505.377163783</v>
+        <v>6785598</v>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3410,27 +3135,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spridd och riklig i området</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3439,75 +3159,76 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111491685</v>
+        <v>108741957</v>
       </c>
       <c r="B25" t="n">
-        <v>88819</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5685</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Stampvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491909.4940688942</v>
+        <v>492030</v>
       </c>
       <c r="R25" t="n">
-        <v>6785494.484901348</v>
+        <v>6785571</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3531,22 +3252,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3555,56 +3276,50 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111491649</v>
+        <v>111491657</v>
       </c>
       <c r="B26" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3617,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491979.6153062462</v>
+        <v>491946</v>
       </c>
       <c r="R26" t="n">
-        <v>6785548.307010972</v>
+        <v>6785571</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3650,24 +3365,14 @@
           <t>2023-08-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-08-15</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>vid bohål</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3695,15 +3400,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111612720</v>
+        <v>107034063</v>
       </c>
       <c r="B27" t="n">
-        <v>88924</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3711,44 +3411,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>256703</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491993.9996831641</v>
+        <v>491909</v>
       </c>
       <c r="R27" t="n">
-        <v>6785505.377163783</v>
+        <v>6785441</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3772,22 +3468,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3803,27 +3489,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111612738</v>
+        <v>111682652</v>
       </c>
       <c r="B28" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3831,31 +3512,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3863,10 +3539,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491952.3910193561</v>
+        <v>492025</v>
       </c>
       <c r="R28" t="n">
-        <v>6785464.984647369</v>
+        <v>6785567</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3893,22 +3569,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3917,6 +3588,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3935,53 +3607,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111612726</v>
+        <v>111356613</v>
       </c>
       <c r="B29" t="n">
-        <v>90168</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>717</v>
+        <v>5685</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Långtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491952.3910193561</v>
+        <v>491932</v>
       </c>
       <c r="R29" t="n">
-        <v>6785464.984647369</v>
+        <v>6785482</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4008,22 +3672,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4032,66 +3686,55 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111612736</v>
+        <v>111491685</v>
       </c>
       <c r="B30" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4099,13 +3742,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491952</v>
+        <v>491909</v>
       </c>
       <c r="R30" t="n">
-        <v>6785465</v>
+        <v>6785494</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4129,12 +3772,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4143,6 +3786,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4161,37 +3805,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111682769</v>
+        <v>111682658</v>
       </c>
       <c r="B31" t="n">
-        <v>89980</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1179</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4204,10 +3843,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491952</v>
+        <v>492025</v>
       </c>
       <c r="R31" t="n">
-        <v>6785465</v>
+        <v>6785567</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4242,6 +3881,11 @@
           <t>2023-08-25</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4251,21 +3895,6 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4282,15 +3911,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111682658</v>
+        <v>112045414</v>
       </c>
       <c r="B32" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4316,22 +3940,25 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492025</v>
+        <v>492045</v>
       </c>
       <c r="R32" t="n">
-        <v>6785567</v>
+        <v>6785564</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4355,17 +3982,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4374,34 +4006,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111682652</v>
+        <v>112045459</v>
       </c>
       <c r="B33" t="n">
-        <v>90709</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4409,40 +4035,47 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Stampvasseln, Stampvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492024</v>
+        <v>492008</v>
       </c>
       <c r="R33" t="n">
-        <v>6785567</v>
+        <v>6785598</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4466,17 +4099,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4485,79 +4123,69 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111682655</v>
+        <v>107034047</v>
       </c>
       <c r="B34" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långtjärnen-Ångvasslan, Dlr</t>
+          <t>Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492025</v>
+        <v>492005</v>
       </c>
       <c r="R34" t="n">
-        <v>6785567</v>
+        <v>6785554</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4581,17 +4209,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4607,49 +4230,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111682665</v>
+        <v>111491662</v>
       </c>
       <c r="B35" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4662,13 +4280,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492024</v>
+        <v>491970</v>
       </c>
       <c r="R35" t="n">
-        <v>6785567</v>
+        <v>6785524</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4692,17 +4310,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Längs stigen/traktorspåret strax utanför gränsmarkeringen som syns på träden</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4730,54 +4343,51 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112045406</v>
+        <v>132252534</v>
       </c>
       <c r="B36" t="n">
-        <v>90831</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>6459</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
+          <t>Stampvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492044</v>
+        <v>492068</v>
       </c>
       <c r="R36" t="n">
-        <v>6785564</v>
+        <v>6785580</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4801,22 +4411,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4827,67 +4427,84 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
+          <t>Anton Björk, Agnes Rengren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112045302</v>
+        <v>111491680</v>
       </c>
       <c r="B37" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492044</v>
+        <v>491930</v>
       </c>
       <c r="R37" t="n">
-        <v>6785564</v>
+        <v>6785530</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4914,22 +4531,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4944,27 +4551,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112073422</v>
+        <v>111612738</v>
       </c>
       <c r="B38" t="n">
-        <v>89098</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4972,43 +4574,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>233195</v>
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria neoformosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>sensu Schild</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N om Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491996</v>
+        <v>491952</v>
       </c>
       <c r="R38" t="n">
-        <v>6785531</v>
+        <v>6785465</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5032,12 +4636,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5046,54 +4650,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112073630</v>
+        <v>108741490</v>
       </c>
       <c r="B39" t="n">
-        <v>89073</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5101,48 +4679,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>256703</v>
+        <v>100077</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N om Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Stampvasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491917</v>
+        <v>492083</v>
       </c>
       <c r="R39" t="n">
-        <v>6785497</v>
+        <v>6785550</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5166,12 +4739,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5180,98 +4763,74 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112045414</v>
+        <v>131607695</v>
       </c>
       <c r="B40" t="n">
-        <v>90838</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56783</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>100077</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen (Nedre Tetvasseltjärnen), Dlr</t>
+          <t>Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492044</v>
+        <v>492048</v>
       </c>
       <c r="R40" t="n">
-        <v>6785564</v>
+        <v>6785388</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5295,22 +4854,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2002-11-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2002-11-23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5325,22 +4874,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128919219</v>
+        <v>111612736</v>
       </c>
       <c r="B41" t="n">
-        <v>92823</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,34 +4897,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491914</v>
+        <v>491952</v>
       </c>
       <c r="R41" t="n">
-        <v>6785535</v>
+        <v>6785465</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5402,12 +4959,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5422,60 +4979,70 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Björk, Agnes Rengren</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129335247</v>
+        <v>55395958</v>
       </c>
       <c r="B42" t="n">
-        <v>90625</v>
+        <v>5179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Övre Tetvasseltjärnen, Dlr</t>
+          <t>strandskog vid Nedre Tetvasseltjärn, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491964</v>
+        <v>492128</v>
       </c>
       <c r="R42" t="n">
-        <v>6785555</v>
+        <v>6785377</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5499,12 +5066,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2015-10-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2015-10-02</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>ÅGP-inventering tallinsekter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5515,26 +5087,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Agnes Rengren, Anton Björk</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132837441</v>
+        <v>107038513</v>
       </c>
       <c r="B43" t="n">
-        <v>101340</v>
+        <v>5179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5542,46 +5119,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stampvasseln vid Nedre Tetvasseltjärnen, Dlr</t>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492106</v>
+        <v>492094</v>
       </c>
       <c r="R43" t="n">
-        <v>6785401</v>
+        <v>6785384</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5605,22 +5182,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>19:31</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>19:31</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5629,21 +5196,1699 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>111491538</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>492032</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6785406</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>55395957</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>strandskog vid Nedre Tetvasseltjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>492128</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6785377</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2015-10-02</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2015-10-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ÅGP-inventering tallinsekter</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>gammal gran med grova grenar</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>107034010</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ångvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>492062</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6785518</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-02-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-02-26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>107034045</v>
+      </c>
+      <c r="B47" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ångvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>492005</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6785554</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-02-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-02-26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>107034168</v>
+      </c>
+      <c r="B48" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Nedre Tetvasseltjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>491933</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6785468</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-02-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-02-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>111491634</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Långtjärnen-Ångvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>492032</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6785406</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>111491490</v>
+      </c>
+      <c r="B50" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Ångvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>492105</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6785454</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>111356614</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>491909</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6785498</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>111359889</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>491909</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6785498</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>84956658</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Ångvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>492105</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6785454</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Barbro Hellström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132837441</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stampvasseln vid Nedre Tetvasseltjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>492106</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6785401</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
           <t>Uno Skog</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
+      <c r="AX54" t="inlineStr">
         <is>
           <t>Uno Skog</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>112073422</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91426</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>233195</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ramaria neoformosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>sensu Schild</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>N om Nedre Tetvasseltjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>491996</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6785531</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>112045739</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stampvasseln, Stampvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>492008</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6785598</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Bengt Oldhammer, Janolof Hermansson, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>112073625</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>N om Nedre Tetvasseltjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>492041</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6785576</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>112073630</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>N om Nedre Tetvasseltjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>491917</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6785498</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-09-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Bengt Oldhammer, Bo karlstens, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1135-2023 artfynd.xlsx
+++ b/artfynd/A 1135-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107034197</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111612726</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045817</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111682769</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53739398</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84489811</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84956522</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1564,6 +1604,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84956539</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108742808</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1807,6 +1857,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132360245</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1904,6 +1959,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918470</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,6 +2061,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129335247</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111682665</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045406</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2325,6 +2400,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111682655</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2433,6 +2513,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045302</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2550,6 +2635,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045425</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2647,6 +2737,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128919219</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2748,6 +2843,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356612</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2854,6 +2954,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491649</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2960,6 +3065,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491681</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3057,6 +3167,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918765</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3174,6 +3289,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045503</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3291,6 +3411,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108741957</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3397,6 +3522,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491657</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3498,6 +3628,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107034063</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3604,6 +3739,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111682652</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3701,6 +3841,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356613</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3802,6 +3947,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491685</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3908,6 +4058,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111682658</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4021,6 +4176,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045414</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4138,6 +4298,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045459</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4239,6 +4404,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107034047</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4340,6 +4510,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491662</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4455,6 +4630,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132252534</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4560,6 +4740,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491680</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4665,6 +4850,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111612738</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4778,6 +4968,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108741490</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4883,6 +5078,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131607695</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4988,6 +5188,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111612736</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5105,6 +5310,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55395958</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5212,6 +5422,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107038513</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5319,6 +5534,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491538</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5436,6 +5656,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55395957</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5543,6 +5768,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107034010</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5650,6 +5880,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107034045</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5757,6 +5992,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107034168</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5864,6 +6104,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491634</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5975,6 +6220,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491490</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6076,6 +6326,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356614</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6178,6 +6433,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111359889</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6280,6 +6540,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84956658</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6396,6 +6661,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132837441</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6520,6 +6790,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073422</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6631,6 +6906,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112045739</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6760,6 +7040,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073625</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6889,8 +7174,72 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112073630</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>